--- a/demo/心桥_全功能演示导入模板.xlsx
+++ b/demo/心桥_全功能演示导入模板.xlsx
@@ -1510,7 +1510,7 @@
         <v>欧阳先生</v>
       </c>
       <c r="C35" s="1">
-        <v>46283</v>
+        <v>32404</v>
       </c>
       <c r="D35" t="str">
         <v>男</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">  · 生日混用 8 种格式：1990-08-05、08-12、1979/08/10、1987.08.20、1990年8月5日、8月5日、8-11、Excel 日期序列号（欧阳先生 2026-09-18），导入时系统自动识别并统一转换。</v>
+        <v xml:space="preserve">  · 生日混用 8 种格式：1990-08-05、08-12、1979/08/10、1987.08.20、1990年8月5日、8月5日、8-11、Excel 日期序列号（欧阳先生 1988-09-18），导入时系统自动识别并统一转换。</v>
       </c>
     </row>
     <row r="16">

--- a/demo/心桥_全功能演示导入模板.xlsx
+++ b/demo/心桥_全功能演示导入模板.xlsx
@@ -1575,7 +1575,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">  · 今日生日 5 位（2026-08-05），可演示“今日生日”卡片、完成维护与当天提醒（A 类：刘先生、陈先生）；</v>
+        <v xml:space="preserve">  · 今日生日 5 位（2026-08-05），可演示“今日生日”卡片与完成维护（当天提醒暂缓上线）；</v>
       </c>
     </row>
     <row r="7">
